--- a/BeatnotePostHotCell/AllFitsF1=4_playing with.xlsx
+++ b/BeatnotePostHotCell/AllFitsF1=4_playing with.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306C28B2-C533-4069-94C2-E0659F9677F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABB8FD0-1C31-406C-9063-24AEF1C5B3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Together" sheetId="1" r:id="rId1"/>
@@ -2904,4252 +2904,6 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>5-Jun</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'All Together'!$B$32:$B$36</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>8.2927304597387206</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>8.5895120122534792</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.6524212475503699</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.4368095561837997</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8.6554109919161206</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'All Together'!$C$32:$C$36</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.108110401129387</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.110683626430072</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.110618484823125</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.110098201353416</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.111279548853152</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-826F-4FA0-8179-ABD436AA34BC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>10-Jun</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'All Together'!$B$57:$B$88</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
-                <c:pt idx="0">
-                  <c:v>7.0733851626533504</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>7.0645821415754702</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.0594232243202404</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7.0595369414161802</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.1355028757261403</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7.1742988315936698</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7.2143004246012596</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7.1896716464449897</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7.0740088746791701</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>7.1243444840245997</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>7.0585349758452001</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>7.0753396553470003</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>7.0929763944296802</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>7.1058506533772503</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>7.1002899790140797</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7.0521776395148397</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>7.1167399746803</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>7.1150966196750796</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7.1580456374110897</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7.2190634878376496</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>7.2062880356903998</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>7.1744031277414697</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>7.1782561712895996</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>7.1789296294298</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>7.1380410516405304</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>7.1009576964689503</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>7.1095475512566804</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>7.1520505928297498</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>7.1324554911158904</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>7.1772995060305798</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>7.13962874760949</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>7.1606128880127899</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'All Together'!$C$57:$C$88</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
-                <c:pt idx="0">
-                  <c:v>9.1307178056809907E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9.0851652530901106E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.0871105956180601E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>9.1887059128850701E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>9.0625181514815994E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>9.19073278180111E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>9.16991502213306E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>9.2126787185543096E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9.2487262159234904E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9.2057197677155297E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>9.0785728319137698E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>9.1583374078481494E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9.1977352407887902E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>9.0809253307868806E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>9.2274633741869796E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>9.1163861413001701E-2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>9.1080103179609503E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>9.1489922352594399E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>9.24749435955321E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>9.2335401313700993E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>9.1016046887435004E-2</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>9.1793854609833803E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>9.0459757856193396E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>9.0535769763873494E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>9.2308774170074298E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>9.169315182519E-2</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>9.0973320989362394E-2</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>9.2289486690982594E-2</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>9.2332804146897596E-2</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>9.1338576946075195E-2</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>9.2043650053371201E-2</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>9.2039900597932794E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-826F-4FA0-8179-ABD436AA34BC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>11-Jun</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'All Together'!$B$89:$B$104</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
-                <c:pt idx="0">
-                  <c:v>5.5657944042335004</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.4648667593817297</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.6047427761818804</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.5960936640263199</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.4713363021862502</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5.5409104673644096</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>5.55013048416959</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>5.5616342974163304</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>5.5301083552827803</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>5.4935494282478201</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5.4627011461568502</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.5557750287565701</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5.5014512688728496</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5.4947589504036598</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5.5489303201094904</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>5.4160645106972503</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'All Together'!$C$89:$C$104</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
-                <c:pt idx="0">
-                  <c:v>6.9580113040116104E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>7.0068196646880104E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.0994631005327505E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7.01413654005653E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.1625188956317504E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7.04951567436682E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7.1076737537177401E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7.0296602179900303E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7.0157369715004997E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>7.0955354830624304E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>7.0402355659330701E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>6.9408807064024997E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>7.0420029676822898E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>7.1119616242477604E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>6.8778607126876098E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6.9985374084186203E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-826F-4FA0-8179-ABD436AA34BC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:v>12-Jun</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'All Together'!$B$105:$B$140</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
-                <c:pt idx="0">
-                  <c:v>13.881207281537201</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>14.0895904209866</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>13.781524940490501</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>13.849983967959</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>14.1045893865774</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>14.045243904631301</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>14.041948410297801</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>13.9314720937797</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>13.939302031872</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>13.7686312681289</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>13.860947786333201</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>14.0288192886568</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>14.0564949797</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>13.967021506007001</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>13.8984865800428</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>13.7709959964952</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>13.7843547051184</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>13.808475282008599</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>14.015153400719299</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>14.0254740862873</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>13.9997618436749</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>14.019342208389499</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>13.970695398759901</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>13.907971630891801</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>13.8994236879669</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>14.055169741167299</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>13.9142762890247</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>13.841323444683701</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>13.804980095407201</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>13.884446951227901</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>13.963402223733601</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>13.9597270287277</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>13.946102058433601</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>13.9823014618208</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>13.749906400784599</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>13.720594247384501</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'All Together'!$C$105:$C$140</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
-                <c:pt idx="0">
-                  <c:v>0.174179408135331</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.177774925130529</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.17240658415385299</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.17600471089717301</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.17541168833131099</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.178859466811089</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.17693051626013501</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.17354864156647201</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.17834649689539001</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.17586320937466099</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.180271615500876</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.17487871734820501</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.18107037027506301</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.17968547629579501</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.17831650497979901</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.17606881780824499</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.179066023936296</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.177536328461042</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.17700590462459101</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.176845695868282</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.17772123501191101</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.17485108835940399</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.174086444253885</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.17721978032439201</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.177247013055988</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.17554660297643901</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.176832773520505</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.178312428161159</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.17923862445315999</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.17704529946634301</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.17678671405309901</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.173286761817802</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.17732355138347</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.17497871224561701</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.17569336443192901</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.17739676585251099</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-826F-4FA0-8179-ABD436AA34BC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:v>15-Jun</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'All Together'!$B$141:$B$171</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
-                <c:pt idx="0">
-                  <c:v>15.5831740366148</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>15.6181213588261</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>15.471660411280601</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>15.4286358328345</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>15.725390191826</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>15.6295450777592</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>15.5447105698267</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>15.641779033917301</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>15.560241393406899</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>15.6798903930978</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>15.5257705053734</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>15.5068553708303</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>15.7245514226287</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>15.653971830187899</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15.585241971938</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>15.591441713773801</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>15.513624662526899</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>15.550450799138201</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>15.5999990421973</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>15.5612294230614</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>15.389959627991299</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>15.6769168147221</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>15.516217850365001</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>15.4712021433598</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>15.4267437621642</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>15.363023447442201</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>15.4784018893041</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>15.598700910453401</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>15.699463941581101</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>15.751226314712399</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>15.601321813860199</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'All Together'!$C$141:$C$171</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
-                <c:pt idx="0">
-                  <c:v>0.20299557534608501</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.19731634658855901</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.19499427606217101</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.19929121653023299</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.19845180139427099</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.20114408935894201</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.198751656579995</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.19986305957069</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.19941466362585</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.19974551641855301</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.19734425148693999</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.20451746200448701</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.20186014691704701</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.19616147617243301</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.20141708222610599</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.20570646230981299</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.198433606499996</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.19684836052329399</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.19797213592714</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.19746160960659001</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.201235306306627</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.19609449317179301</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.198095518321387</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.201202131188608</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.19854017174952801</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.20017070885951799</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.19706209535145</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.200682963445732</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.19843356572069301</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.19746491101406</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.201690348999186</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-826F-4FA0-8179-ABD436AA34BC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="6"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:v>16-Jun</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'All Together'!$B$172:$B$194</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
-                <c:pt idx="0">
-                  <c:v>15.893216524612599</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>15.779780400421799</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>15.7375098014318</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>15.644238135424301</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>16.0404007362275</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>15.526853103393799</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>15.7036096357806</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>15.562012023522399</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>15.913642252075</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>15.896285735356299</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>15.958659068376001</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>15.673134901285501</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>15.850053804713101</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>15.8642190956806</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15.9252668940867</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>15.884348606860501</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>15.6346331521121</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>15.818170639051299</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>15.947264131374601</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>15.924948044130501</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>15.963192712237699</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>15.8676552218831</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>15.928435989248699</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'All Together'!$C$171:$C$194</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
-                <c:pt idx="0">
-                  <c:v>0.201690348999186</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.197795261805772</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.19636764328003201</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.199763540533482</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.199521024785556</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.20007723541863701</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.19981867055438399</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.198366202574008</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.199095753907192</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.204499456522232</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.20177332786484001</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.19953623295292</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.20147692004263501</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.20099134894088699</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.20205758915667599</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.19732734762757201</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.203672875007014</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.202463132614286</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.201204039279366</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.19871515752240099</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.19699200110692699</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.19973329976234899</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.201359161151828</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.19777927876332499</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-826F-4FA0-8179-ABD436AA34BC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="7"/>
-          <c:order val="6"/>
-          <c:tx>
-            <c:v>17-Jun</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="60000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'All Together'!$B$195:$B$213</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>10.6515835159838</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10.663341069103801</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.720671290806401</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10.6070403098376</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>10.607916558495299</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10.796548325563</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10.8409786177823</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>10.772956842649499</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>10.6830303352735</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10.585364148466899</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10.5286364956397</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>10.6204309820713</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>10.6162779389606</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>10.775713711424901</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>10.7723544954987</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>10.7080767594852</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>10.6292015876151</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>10.6922490647235</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>10.661460418557301</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'All Together'!$C$195:$C$213</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>0.13468054835968099</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.13679830071593899</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.135403359867214</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.13595989010586099</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.13748020113746301</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.13777383840185101</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.13676101673190699</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.13512046849112699</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.13660109283925101</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.13641311645492901</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.13599421764432501</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.133813897334362</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.13398818137368401</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.135526162232535</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.13583799718759201</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.13529790524896701</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.13334859062780199</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.13491725008311001</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.137631619653904</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-826F-4FA0-8179-ABD436AA34BC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="8"/>
-          <c:order val="7"/>
-          <c:tx>
-            <c:v>18-Jun</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3">
-                    <a:lumMod val="60000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'All Together'!$B$214:$B$228</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>10.794234615893799</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10.8450661689269</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.7513220521733</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10.544390346656099</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>10.7196028974402</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10.753363759575</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10.653749196664901</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>10.8630753057798</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>10.7208205400928</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10.6700806810118</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10.6606574449491</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>10.8131728102025</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>10.8081420366551</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>10.586819027671799</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>10.7337029456849</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'All Together'!$C$214:$C$228</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>0.13803642019148099</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.1328729865195</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.136218398205117</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.13785864233595099</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.13392104624134801</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.13552887551307799</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.137036547539267</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.135737051657839</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.13411786534959899</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.135674971298644</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.13332899819484301</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.13422513879040401</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.14001016382505199</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.135848256649828</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.13795749701744001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000A-826F-4FA0-8179-ABD436AA34BC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="9"/>
-          <c:order val="8"/>
-          <c:tx>
-            <c:v>jun19+Sheet1!$B$229:$B$233</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4">
-                    <a:lumMod val="60000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'All Together'!$B$229:$B$233</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>10.6539096425895</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10.8579810008815</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.831312443746899</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10.709515833036701</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>10.5903781690852</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'All Together'!$C$229:$C$233</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.13307975295074501</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.13372258287568001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.13573289163324301</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.13770965349766401</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.137389858296152</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-826F-4FA0-8179-ABD436AA34BC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="9"/>
-          <c:tx>
-            <c:v>9-Jun</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'All Together'!$B$37:$B$56</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
-                <c:pt idx="0">
-                  <c:v>8.2237273067390202</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>8.26640584418465</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.2614937671479094</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.2121360213246692</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8.3727208112640206</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>8.4364141305933895</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>8.4084015562695207</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8.5099572412062301</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8.4321434520724008</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>8.53551089338964</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>8.4721216638779193</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>8.4953666075608503</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>8.7711252103094601</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>8.5801266895029205</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>8.5783681642005494</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>8.6129268121772302</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>8.6349505815443095</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>8.5827352500219707</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>8.6784045244654298</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>8.5889121451567796</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'All Together'!$C$37:$C$55</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>0.10646467829143701</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.105795464107905</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.10490001345581</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.105180184323224</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.105174704460738</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.107845276012769</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.10723041757134</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.106975307605854</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.11017531562982701</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.110843436967219</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.112083608460584</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.108413166888535</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.112594565947194</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.11282550892309801</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.11287509183430799</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.111589996875832</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.11193460088683201</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.109744902012854</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.112489140212508</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7843-4532-8E8E-8E84875AEA00}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="807517807"/>
-        <c:axId val="807515311"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="807517807"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="807515311"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="807515311"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="807517807"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Alpha 456 vs Alpha 894</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'All Together'!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Alpha 456</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'All Together'!$B$2:$B$233</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="232"/>
-                <c:pt idx="0">
-                  <c:v>8.1314875900026795</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>8.2055994032900799</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.2176590050244904</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.2690216688035498</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8.2739805096279504</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>18.481531830496198</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>18.346083770183299</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>18.452491695077299</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18.351915434355199</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>18.337397032620899</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>18.232394257417202</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>18.415074041865601</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>18.341941017083698</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>18.237027996635099</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>18.531243546545401</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>18.412716855394802</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>18.4923898758226</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18.515382021503999</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>18.391192672959299</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>18.551612310419799</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>18.393990200449998</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>18.450034969079201</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>18.408277105199002</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>8.5701060942568006</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>8.5447049809269604</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>8.4017872832855591</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>8.4035403242380404</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>8.5185527459719204</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>8.5260980793629599</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>8.4894844505278897</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>8.2927304597387206</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>8.5895120122534792</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>8.6524212475503699</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>8.4368095561837997</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>8.6554109919161206</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>8.2237273067390202</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>8.26640584418465</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>8.2614937671479094</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>8.2121360213246692</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>8.3727208112640206</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>8.4364141305933895</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>8.4084015562695207</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>8.5099572412062301</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>8.4321434520724008</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>8.53551089338964</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>8.4721216638779193</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>8.4953666075608503</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>8.7711252103094601</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>8.5801266895029205</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>8.5783681642005494</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>8.6129268121772302</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>8.6349505815443095</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>8.5827352500219707</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>8.6784045244654298</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>8.5889121451567796</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>7.0733851626533504</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>7.0645821415754702</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>7.0594232243202404</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>7.0595369414161802</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>7.1355028757261403</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>7.1742988315936698</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>7.2143004246012596</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>7.1896716464449897</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>7.0740088746791701</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>7.1243444840245997</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>7.0585349758452001</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>7.0753396553470003</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>7.0929763944296802</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>7.1058506533772503</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>7.1002899790140797</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>7.0521776395148397</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>7.1167399746803</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>7.1150966196750796</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>7.1580456374110897</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>7.2190634878376496</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>7.2062880356903998</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>7.1744031277414697</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>7.1782561712895996</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>7.1789296294298</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>7.1380410516405304</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>7.1009576964689503</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>7.1095475512566804</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>7.1520505928297498</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>7.1324554911158904</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>7.1772995060305798</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>7.13962874760949</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>7.1606128880127899</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>5.5657944042335004</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>5.4648667593817297</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>5.6047427761818804</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>5.5960936640263199</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>5.4713363021862502</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>5.5409104673644096</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>5.55013048416959</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>5.5616342974163304</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>5.5301083552827803</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>5.4935494282478201</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>5.4627011461568502</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>5.5557750287565701</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>5.5014512688728496</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>5.4947589504036598</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>5.5489303201094904</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>5.4160645106972503</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>13.881207281537201</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>14.0895904209866</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>13.781524940490501</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>13.849983967959</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>14.1045893865774</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>14.045243904631301</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>14.041948410297801</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>13.9314720937797</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>13.939302031872</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>13.7686312681289</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>13.860947786333201</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>14.0288192886568</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>14.0564949797</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>13.967021506007001</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>13.8984865800428</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>13.7709959964952</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>13.7843547051184</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>13.808475282008599</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>14.015153400719299</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>14.0254740862873</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>13.9997618436749</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>14.019342208389499</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>13.970695398759901</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>13.907971630891801</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>13.8994236879669</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>14.055169741167299</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>13.9142762890247</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>13.841323444683701</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>13.804980095407201</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>13.884446951227901</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>13.963402223733601</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>13.9597270287277</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>13.946102058433601</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>13.9823014618208</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>13.749906400784599</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>13.720594247384501</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>15.5831740366148</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>15.6181213588261</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>15.471660411280601</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>15.4286358328345</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>15.725390191826</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>15.6295450777592</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>15.5447105698267</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>15.641779033917301</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>15.560241393406899</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>15.6798903930978</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>15.5257705053734</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>15.5068553708303</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>15.7245514226287</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>15.653971830187899</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>15.585241971938</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>15.591441713773801</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>15.513624662526899</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>15.550450799138201</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>15.5999990421973</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>15.5612294230614</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>15.389959627991299</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>15.6769168147221</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>15.516217850365001</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>15.4712021433598</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>15.4267437621642</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>15.363023447442201</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>15.4784018893041</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>15.598700910453401</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>15.699463941581101</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>15.751226314712399</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>15.601321813860199</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>15.893216524612599</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>15.779780400421799</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>15.7375098014318</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>15.644238135424301</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>16.0404007362275</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>15.526853103393799</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>15.7036096357806</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>15.562012023522399</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>15.913642252075</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>15.896285735356299</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>15.958659068376001</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>15.673134901285501</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>15.850053804713101</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>15.8642190956806</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>15.9252668940867</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>15.884348606860501</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>15.6346331521121</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>15.818170639051299</c:v>
-                </c:pt>
-                <c:pt idx="188">
-                  <c:v>15.947264131374601</c:v>
-                </c:pt>
-                <c:pt idx="189">
-                  <c:v>15.924948044130501</c:v>
-                </c:pt>
-                <c:pt idx="190">
-                  <c:v>15.963192712237699</c:v>
-                </c:pt>
-                <c:pt idx="191">
-                  <c:v>15.8676552218831</c:v>
-                </c:pt>
-                <c:pt idx="192">
-                  <c:v>15.928435989248699</c:v>
-                </c:pt>
-                <c:pt idx="193">
-                  <c:v>10.6515835159838</c:v>
-                </c:pt>
-                <c:pt idx="194">
-                  <c:v>10.663341069103801</c:v>
-                </c:pt>
-                <c:pt idx="195">
-                  <c:v>10.720671290806401</c:v>
-                </c:pt>
-                <c:pt idx="196">
-                  <c:v>10.6070403098376</c:v>
-                </c:pt>
-                <c:pt idx="197">
-                  <c:v>10.607916558495299</c:v>
-                </c:pt>
-                <c:pt idx="198">
-                  <c:v>10.796548325563</c:v>
-                </c:pt>
-                <c:pt idx="199">
-                  <c:v>10.8409786177823</c:v>
-                </c:pt>
-                <c:pt idx="200">
-                  <c:v>10.772956842649499</c:v>
-                </c:pt>
-                <c:pt idx="201">
-                  <c:v>10.6830303352735</c:v>
-                </c:pt>
-                <c:pt idx="202">
-                  <c:v>10.585364148466899</c:v>
-                </c:pt>
-                <c:pt idx="203">
-                  <c:v>10.5286364956397</c:v>
-                </c:pt>
-                <c:pt idx="204">
-                  <c:v>10.6204309820713</c:v>
-                </c:pt>
-                <c:pt idx="205">
-                  <c:v>10.6162779389606</c:v>
-                </c:pt>
-                <c:pt idx="206">
-                  <c:v>10.775713711424901</c:v>
-                </c:pt>
-                <c:pt idx="207">
-                  <c:v>10.7723544954987</c:v>
-                </c:pt>
-                <c:pt idx="208">
-                  <c:v>10.7080767594852</c:v>
-                </c:pt>
-                <c:pt idx="209">
-                  <c:v>10.6292015876151</c:v>
-                </c:pt>
-                <c:pt idx="210">
-                  <c:v>10.6922490647235</c:v>
-                </c:pt>
-                <c:pt idx="211">
-                  <c:v>10.661460418557301</c:v>
-                </c:pt>
-                <c:pt idx="212">
-                  <c:v>10.794234615893799</c:v>
-                </c:pt>
-                <c:pt idx="213">
-                  <c:v>10.8450661689269</c:v>
-                </c:pt>
-                <c:pt idx="214">
-                  <c:v>10.7513220521733</c:v>
-                </c:pt>
-                <c:pt idx="215">
-                  <c:v>10.544390346656099</c:v>
-                </c:pt>
-                <c:pt idx="216">
-                  <c:v>10.7196028974402</c:v>
-                </c:pt>
-                <c:pt idx="217">
-                  <c:v>10.753363759575</c:v>
-                </c:pt>
-                <c:pt idx="218">
-                  <c:v>10.653749196664901</c:v>
-                </c:pt>
-                <c:pt idx="219">
-                  <c:v>10.8630753057798</c:v>
-                </c:pt>
-                <c:pt idx="220">
-                  <c:v>10.7208205400928</c:v>
-                </c:pt>
-                <c:pt idx="221">
-                  <c:v>10.6700806810118</c:v>
-                </c:pt>
-                <c:pt idx="222">
-                  <c:v>10.6606574449491</c:v>
-                </c:pt>
-                <c:pt idx="223">
-                  <c:v>10.8131728102025</c:v>
-                </c:pt>
-                <c:pt idx="224">
-                  <c:v>10.8081420366551</c:v>
-                </c:pt>
-                <c:pt idx="225">
-                  <c:v>10.586819027671799</c:v>
-                </c:pt>
-                <c:pt idx="226">
-                  <c:v>10.7337029456849</c:v>
-                </c:pt>
-                <c:pt idx="227">
-                  <c:v>10.6539096425895</c:v>
-                </c:pt>
-                <c:pt idx="228">
-                  <c:v>10.8579810008815</c:v>
-                </c:pt>
-                <c:pt idx="229">
-                  <c:v>10.831312443746899</c:v>
-                </c:pt>
-                <c:pt idx="230">
-                  <c:v>10.709515833036701</c:v>
-                </c:pt>
-                <c:pt idx="231">
-                  <c:v>10.5903781690852</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'All Together'!$C$2:$C$233</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="232"/>
-                <c:pt idx="0">
-                  <c:v>0.13284709830915301</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.13179599174591999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.13701539714226199</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.13611960900852699</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.13627945937632699</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.30390235043574698</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.30438419283964002</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.297161130585052</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.30092447877826201</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.30225556251139701</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.30453505035585898</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.29441937543381203</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.29938049893952201</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.30198767465833298</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.29452133244947898</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.30226636207287</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.30276185184620003</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.30565983998385898</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.30235700258888798</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.30470031507930101</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.30681032275950298</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.31003085423784599</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.30130891367381502</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.141175020925183</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.13910706901585701</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.14173595580689399</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.141258173819516</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.142207734258748</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.13801119003128501</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.14302506923553299</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.108110401129387</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.110683626430072</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.110618484823125</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.110098201353416</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.111279548853152</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.10646467829143701</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.105795464107905</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.10490001345581</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.105180184323224</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.105174704460738</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.107845276012769</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.10723041757134</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.106975307605854</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.11017531562982701</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.110843436967219</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.112083608460584</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.108413166888535</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.112594565947194</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.11282550892309801</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.11287509183430799</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.111589996875832</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.11193460088683201</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.109744902012854</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.112489140212508</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.108339261727823</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>9.1307178056809907E-2</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>9.0851652530901106E-2</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>9.0871105956180601E-2</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>9.1887059128850701E-2</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>9.0625181514815994E-2</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>9.19073278180111E-2</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>9.16991502213306E-2</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>9.2126787185543096E-2</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>9.2487262159234904E-2</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>9.2057197677155297E-2</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>9.0785728319137698E-2</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>9.1583374078481494E-2</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>9.1977352407887902E-2</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>9.0809253307868806E-2</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>9.2274633741869796E-2</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>9.1163861413001701E-2</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>9.1080103179609503E-2</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>9.1489922352594399E-2</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>9.24749435955321E-2</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>9.2335401313700993E-2</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>9.1016046887435004E-2</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>9.1793854609833803E-2</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>9.0459757856193396E-2</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>9.0535769763873494E-2</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>9.2308774170074298E-2</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>9.169315182519E-2</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>9.0973320989362394E-2</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>9.2289486690982594E-2</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>9.2332804146897596E-2</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>9.1338576946075195E-2</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>9.2043650053371201E-2</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>9.2039900597932794E-2</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>6.9580113040116104E-2</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>7.0068196646880104E-2</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>7.0994631005327505E-2</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>7.01413654005653E-2</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>7.1625188956317504E-2</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>7.04951567436682E-2</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>7.1076737537177401E-2</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>7.0296602179900303E-2</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>7.0157369715004997E-2</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>7.0955354830624304E-2</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>7.0402355659330701E-2</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>6.9408807064024997E-2</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>7.0420029676822898E-2</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>7.1119616242477604E-2</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>6.8778607126876098E-2</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>6.9985374084186203E-2</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>0.174179408135331</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>0.177774925130529</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>0.17240658415385299</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>0.17600471089717301</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>0.17541168833131099</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>0.178859466811089</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>0.17693051626013501</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>0.17354864156647201</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>0.17834649689539001</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>0.17586320937466099</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>0.180271615500876</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>0.17487871734820501</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>0.18107037027506301</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>0.17968547629579501</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>0.17831650497979901</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>0.17606881780824499</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>0.179066023936296</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>0.177536328461042</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>0.17700590462459101</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>0.176845695868282</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>0.17772123501191101</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>0.17485108835940399</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>0.174086444253885</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>0.17721978032439201</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>0.177247013055988</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>0.17554660297643901</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>0.176832773520505</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>0.178312428161159</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>0.17923862445315999</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>0.17704529946634301</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>0.17678671405309901</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>0.173286761817802</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>0.17732355138347</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>0.17497871224561701</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>0.17569336443192901</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>0.17739676585251099</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>0.20299557534608501</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>0.19731634658855901</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>0.19499427606217101</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>0.19929121653023299</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>0.19845180139427099</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>0.20114408935894201</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>0.198751656579995</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>0.19986305957069</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>0.19941466362585</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>0.19974551641855301</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>0.19734425148693999</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>0.20451746200448701</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>0.20186014691704701</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>0.19616147617243301</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>0.20141708222610599</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>0.20570646230981299</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>0.198433606499996</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>0.19684836052329399</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>0.19797213592714</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>0.19746160960659001</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>0.201235306306627</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>0.19609449317179301</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>0.198095518321387</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>0.201202131188608</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>0.19854017174952801</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>0.20017070885951799</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>0.19706209535145</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>0.200682963445732</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>0.19843356572069301</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>0.19746491101406</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>0.201690348999186</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>0.197795261805772</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>0.19636764328003201</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>0.199763540533482</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>0.199521024785556</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>0.20007723541863701</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>0.19981867055438399</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>0.198366202574008</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>0.199095753907192</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>0.204499456522232</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>0.20177332786484001</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>0.19953623295292</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>0.20147692004263501</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>0.20099134894088699</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>0.20205758915667599</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>0.19732734762757201</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>0.203672875007014</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>0.202463132614286</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>0.201204039279366</c:v>
-                </c:pt>
-                <c:pt idx="188">
-                  <c:v>0.19871515752240099</c:v>
-                </c:pt>
-                <c:pt idx="189">
-                  <c:v>0.19699200110692699</c:v>
-                </c:pt>
-                <c:pt idx="190">
-                  <c:v>0.19973329976234899</c:v>
-                </c:pt>
-                <c:pt idx="191">
-                  <c:v>0.201359161151828</c:v>
-                </c:pt>
-                <c:pt idx="192">
-                  <c:v>0.19777927876332499</c:v>
-                </c:pt>
-                <c:pt idx="193">
-                  <c:v>0.13468054835968099</c:v>
-                </c:pt>
-                <c:pt idx="194">
-                  <c:v>0.13679830071593899</c:v>
-                </c:pt>
-                <c:pt idx="195">
-                  <c:v>0.135403359867214</c:v>
-                </c:pt>
-                <c:pt idx="196">
-                  <c:v>0.13595989010586099</c:v>
-                </c:pt>
-                <c:pt idx="197">
-                  <c:v>0.13748020113746301</c:v>
-                </c:pt>
-                <c:pt idx="198">
-                  <c:v>0.13777383840185101</c:v>
-                </c:pt>
-                <c:pt idx="199">
-                  <c:v>0.13676101673190699</c:v>
-                </c:pt>
-                <c:pt idx="200">
-                  <c:v>0.13512046849112699</c:v>
-                </c:pt>
-                <c:pt idx="201">
-                  <c:v>0.13660109283925101</c:v>
-                </c:pt>
-                <c:pt idx="202">
-                  <c:v>0.13641311645492901</c:v>
-                </c:pt>
-                <c:pt idx="203">
-                  <c:v>0.13599421764432501</c:v>
-                </c:pt>
-                <c:pt idx="204">
-                  <c:v>0.133813897334362</c:v>
-                </c:pt>
-                <c:pt idx="205">
-                  <c:v>0.13398818137368401</c:v>
-                </c:pt>
-                <c:pt idx="206">
-                  <c:v>0.135526162232535</c:v>
-                </c:pt>
-                <c:pt idx="207">
-                  <c:v>0.13583799718759201</c:v>
-                </c:pt>
-                <c:pt idx="208">
-                  <c:v>0.13529790524896701</c:v>
-                </c:pt>
-                <c:pt idx="209">
-                  <c:v>0.13334859062780199</c:v>
-                </c:pt>
-                <c:pt idx="210">
-                  <c:v>0.13491725008311001</c:v>
-                </c:pt>
-                <c:pt idx="211">
-                  <c:v>0.137631619653904</c:v>
-                </c:pt>
-                <c:pt idx="212">
-                  <c:v>0.13803642019148099</c:v>
-                </c:pt>
-                <c:pt idx="213">
-                  <c:v>0.1328729865195</c:v>
-                </c:pt>
-                <c:pt idx="214">
-                  <c:v>0.136218398205117</c:v>
-                </c:pt>
-                <c:pt idx="215">
-                  <c:v>0.13785864233595099</c:v>
-                </c:pt>
-                <c:pt idx="216">
-                  <c:v>0.13392104624134801</c:v>
-                </c:pt>
-                <c:pt idx="217">
-                  <c:v>0.13552887551307799</c:v>
-                </c:pt>
-                <c:pt idx="218">
-                  <c:v>0.137036547539267</c:v>
-                </c:pt>
-                <c:pt idx="219">
-                  <c:v>0.135737051657839</c:v>
-                </c:pt>
-                <c:pt idx="220">
-                  <c:v>0.13411786534959899</c:v>
-                </c:pt>
-                <c:pt idx="221">
-                  <c:v>0.135674971298644</c:v>
-                </c:pt>
-                <c:pt idx="222">
-                  <c:v>0.13332899819484301</c:v>
-                </c:pt>
-                <c:pt idx="223">
-                  <c:v>0.13422513879040401</c:v>
-                </c:pt>
-                <c:pt idx="224">
-                  <c:v>0.14001016382505199</c:v>
-                </c:pt>
-                <c:pt idx="225">
-                  <c:v>0.135848256649828</c:v>
-                </c:pt>
-                <c:pt idx="226">
-                  <c:v>0.13795749701744001</c:v>
-                </c:pt>
-                <c:pt idx="227">
-                  <c:v>0.13307975295074501</c:v>
-                </c:pt>
-                <c:pt idx="228">
-                  <c:v>0.13372258287568001</c:v>
-                </c:pt>
-                <c:pt idx="229">
-                  <c:v>0.13573289163324301</c:v>
-                </c:pt>
-                <c:pt idx="230">
-                  <c:v>0.13770965349766401</c:v>
-                </c:pt>
-                <c:pt idx="231">
-                  <c:v>0.137389858296152</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4BD7-4F63-BC7F-C2C55BDA6A19}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>new</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'All Together'!$B$235:$B$296</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
-                <c:pt idx="0">
-                  <c:v>10.6221259181231</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10.735748783007899</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.566758158407101</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10.631078078007899</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>10.634659592750699</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10.672389702778499</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10.624260123408201</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>10.518782041710701</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>10.635277697575599</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10.703364754206801</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10.6888204197401</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>10.707744909524299</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>10.731647561909099</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>10.743488692224201</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>10.7190641789712</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>10.7246119730962</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>10.854434693120901</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>10.706374987729699</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>10.637698363317099</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>10.739175433178</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>10.686605164880801</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>10.6515045746171</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>10.701321936698699</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>10.605269760878899</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>10.5803727434901</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>10.576268807422901</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>10.5196221348473</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>10.558405934335401</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>10.633836662036201</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>10.6134173334769</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>10.660587486404401</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>16.4455493987636</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>16.204494346869399</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>16.286326741643599</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>16.207702786854899</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>16.458700382311001</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>16.462078937325401</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>16.471494559838</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>16.339485818946901</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>16.355055381852601</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>16.3595891765879</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>16.2164791072151</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>16.261548141097599</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>16.384810735183699</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>16.350623841514199</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>16.187723396986499</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>16.3038309514011</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>16.164613922247401</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>16.240097105116</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>16.2518971233978</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>16.381371335960701</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>16.378295734472999</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>16.444871536786899</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>16.377685606618101</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>16.370821349538001</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>16.147989198104199</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>16.418772327555299</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>16.352237501405199</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>16.311710862235199</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>16.368589028451201</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>16.289962255694199</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>16.347944436289598</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'All Together'!$C$235:$C$296</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
-                <c:pt idx="0">
-                  <c:v>0.171876620266287</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.17507983789020901</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.17353748848485201</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.17399520336378199</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.16979104098602099</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.175682517244173</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.17111359499762699</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.174442312499583</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.17165345419397299</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.17188594050678699</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.17182639857690499</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.173011271970926</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.173393882992014</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.17255170638235601</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.176156057962948</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.17277891898827699</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.173614948750792</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.17607067167010601</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.17040120856414201</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.17423160269966501</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.174369956316375</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.17111424613243301</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.174141819699693</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.17027613633024699</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.17305899861083601</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.169629744786672</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.17362236751906199</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.17378947989454699</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.17301730214639</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.17294290042990301</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.17314296764265499</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.26702709086345899</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.26377604366503299</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.26272554597887199</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.26788317969509901</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.26503400399869398</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.26673897966627602</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.26807575946030698</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.266570039729353</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.27166172606546901</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.26522605962651602</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.27094063293660098</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.26838563360762802</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.26226006746867903</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.26283415625491802</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.265891536409124</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.26086999753535101</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.264030412441006</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.26104421609513101</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.26790761730572898</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.26200964452208297</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.26657014430711701</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.264335730958146</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.26876048744697101</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.26514897700620299</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.26219390887345601</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.26184487099436499</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.26409583467590397</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.26424448419416702</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.26363414452799</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.26464837628465498</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.27030866825799199</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-4BD7-4F63-BC7F-C2C55BDA6A19}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="9231519"/>
-        <c:axId val="9232479"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="9231519"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>894 Coefficient</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="9232479"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="9232479"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>456 Coefficient</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="9231519"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
     <c:title>
       <c:overlay val="0"/>
       <c:spPr>
@@ -9110,7 +4864,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -9518,7 +5272,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -12098,7 +7852,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -12760,86 +8514,6 @@
 </file>
 
 <file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -15459,1038 +11133,6 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -16524,80 +11166,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>206854</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>305521</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>197329</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>569885</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7787F323-BD16-42B2-A599-D2F79A0A6C2E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>530165</xdr:colOff>
-      <xdr:row>246</xdr:row>
-      <xdr:rowOff>44929</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>125802</xdr:colOff>
-      <xdr:row>258</xdr:row>
-      <xdr:rowOff>149762</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Chart 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A62A320E-B8E2-4608-BC93-F68B614A6BB2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
